--- a/web/public/forms/orig/o-chakgong-moeum.xlsx
+++ b/web/public/forms/orig/o-chakgong-moeum.xlsx
@@ -1280,7 +1280,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1943,7 +1943,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3847,7 +3847,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4847,7 +4847,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -5501,7 +5501,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -6330,7 +6330,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -7218,7 +7218,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
@@ -7728,7 +7728,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
@@ -8313,7 +8313,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
@@ -8901,7 +8901,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -9482,7 +9482,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -10579,7 +10579,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -11239,7 +11239,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="148" t="inlineStr">
@@ -12001,7 +12001,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="148" t="inlineStr">
@@ -12627,7 +12627,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="148" t="inlineStr">
@@ -13054,7 +13054,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="148" t="inlineStr">
@@ -13416,7 +13416,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="148" t="inlineStr">
@@ -13921,7 +13921,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="148" t="inlineStr">
@@ -14069,7 +14069,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="148" t="inlineStr">
@@ -14299,7 +14299,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="148" t="inlineStr">
@@ -14639,7 +14639,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -15066,7 +15066,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="148" t="inlineStr">
@@ -15571,7 +15571,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="148" t="inlineStr">
@@ -17530,7 +17530,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="148" t="inlineStr">
@@ -18221,7 +18221,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="148" t="inlineStr">
@@ -18562,7 +18562,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="148" t="inlineStr">
@@ -19217,7 +19217,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="148" t="inlineStr">
@@ -20059,7 +20059,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="148" t="inlineStr">
@@ -20400,7 +20400,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="148" t="inlineStr">
@@ -20949,7 +20949,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="I1" s="148" t="inlineStr">
@@ -21484,7 +21484,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="I1" s="148" t="inlineStr">
@@ -22150,7 +22150,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -22517,7 +22517,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="I1" s="148" t="inlineStr">
@@ -23164,7 +23164,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="148" t="inlineStr">
@@ -24274,7 +24274,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="148" t="inlineStr">
@@ -24929,7 +24929,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -25433,7 +25433,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -25580,7 +25580,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -25809,7 +25809,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -26149,7 +26149,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">

--- a/web/public/forms/orig/o-chakgong-moeum.xlsx
+++ b/web/public/forms/orig/o-chakgong-moeum.xlsx
@@ -1216,7 +1216,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4298,7 +4298,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -5975,7 +5975,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -6775,7 +6775,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
@@ -7221,7 +7221,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
@@ -7654,7 +7654,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
@@ -8090,7 +8090,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -8589,7 +8589,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -9675,7 +9675,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -10284,7 +10284,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -10651,7 +10651,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -10968,7 +10968,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -11470,7 +11470,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -11603,7 +11603,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -11815,7 +11815,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -12117,7 +12117,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
